--- a/sampleprojects/CorporateTax/excel/states/KS_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/KS_corp.xlsx
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($100K gross receipts or 200 transactions); result.ks_gross_receipts is greater than or equal to result.ks_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.ks_gross_receipts &gt;= result.ks_economic_nexus_threshold</t>
+    <t>ks_result.gross_receipts &gt;= ks_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.ks_has_nexus = true;</t>
+    <t>set ks_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.ks_has_nexus = false; set result.ks_tax_liability = 0.0;</t>
+    <t>set ks_result.has_nexus = false; set ks_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate KS Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Kansas nexus</t>
   </si>
   <si>
-    <t>result.ks_has_nexus is equal to true</t>
+    <t>ks_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Kansas state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.ks_state_additions = 0.0; if result.ks_us_interest_income != 0.0 then set result.ks_state_additions = result.ks_state_additions + result.ks_us_interest_income; endif if result.ks_state_tax_refunds != 0.0 then set result.ks_state_additions = result.ks_state_additions + result.ks_state_tax_refunds; endif set result.ks_state_subtractions = 0.0; if result.ks_municipal_interest != 0.0 then set result.ks_state_subtractions = result.ks_state_subtractions + result.ks_municipal_interest; endif if result.ks_state_taxes_paid != 0.0 then set result.ks_state_subtractions = result.ks_state_subtractions + result.ks_state_taxes_paid; endif add (("Kansas additions: $" + string value of (result.ks_state_additions)) + ", subtractions: $") + string value of (result.ks_state_subtractions) to job.audit_trail;</t>
+    <t>set ks_result.state_additions = 0.0; if ks_result.us_interest_income != 0.0 then set ks_result.state_additions = ks_result.state_additions + ks_result.us_interest_income; endif if ks_result.state_tax_refunds != 0.0 then set ks_result.state_additions = ks_result.state_additions + ks_result.state_tax_refunds; endif set ks_result.state_subtractions = 0.0; if ks_result.municipal_interest != 0.0 then set ks_result.state_subtractions = ks_result.state_subtractions + ks_result.municipal_interest; endif if ks_result.state_taxes_paid != 0.0 then set ks_result.state_subtractions = ks_result.state_subtractions + ks_result.state_taxes_paid; endif add (("Kansas additions: $" + string value of (ks_result.state_additions)) + ", subtractions: $") + string value of (ks_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.ks_state_additions = 0.0; set result.ks_state_subtractions = 0.0;</t>
+    <t>set ks_result.state_additions = 0.0; set ks_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate KS State Tax</t>
@@ -145,31 +145,31 @@
     <t>Has positive taxable income; result.ks_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.ks_apportioned_income &gt; 0.0</t>
+    <t>ks_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Income exceeds $50,000 surtax threshold; result.ks_taxable_income is greater than result.ks_surtax_threshold</t>
   </si>
   <si>
-    <t>result.ks_taxable_income &gt; result.ks_surtax_threshold</t>
+    <t>ks_result.taxable_income &gt; ks_result.surtax_threshold</t>
   </si>
   <si>
     <t>Calculate Kansas tax with base rate + surtax (income over $50K); Apply 4.0% base + 3.0% surtax on income over $50K</t>
   </si>
   <si>
-    <t>set result.ks_taxable_income = the maximum of (result.ks_apportioned_income + result.ks_state_additions - result.ks_state_subtractions) and (0.0); set result.ks_base_tax = result.ks_taxable_income * result.ks_corp_tax_base_rate; set result.ks_surtax = (result.ks_taxable_income - result.ks_surtax_threshold) * result.ks_corp_tax_surtax_rate; set result.ks_tax_liability = the maximum of (result.ks_base_tax + result.ks_surtax - result.ks_state_credits) and (0.0); set result.ks_refund_or_owed = result.ks_estimated_payments - result.ks_tax_liability; add "Kansas taxable income: $" + string value of (result.ks_taxable_income) to job.audit_trail; add "Kansas base tax (4.0%): $" + string value of (result.ks_base_tax) to job.audit_trail; add "Kansas surtax (3.0% on excess over $50K): $" + string value of (result.ks_surtax) to job.audit_trail; add "Kansas tax liability: $" + string value of (result.ks_tax_liability) to job.audit_trail;</t>
+    <t>set ks_result.taxable_income = the maximum of (ks_result.apportioned_income + ks_result.state_additions - ks_result.state_subtractions) and (0.0); set ks_result.base_tax = ks_result.taxable_income * ks_result.corp_tax_base_rate; set ks_result.surtax = (ks_result.taxable_income - ks_result.surtax_threshold) * ks_result.corp_tax_surtax_rate; set ks_result.tax_liability = the maximum of (ks_result.base_tax + ks_result.surtax - ks_result.state_credits) and (0.0); set ks_result.refund_or_owed = ks_result.estimated_payments - ks_result.tax_liability; add "Kansas taxable income: $" + string value of (ks_result.taxable_income) to job.audit_trail; add "Kansas base tax (4.0%): $" + string value of (ks_result.base_tax) to job.audit_trail; add "Kansas surtax (3.0% on excess over $50K): $" + string value of (ks_result.surtax) to job.audit_trail; add "Kansas tax liability: $" + string value of (ks_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>Calculate Kansas tax - income $50K or less (base rate only); Apply only 4.0% base rate</t>
   </si>
   <si>
-    <t>set result.ks_taxable_income = the maximum of (result.ks_apportioned_income + result.ks_state_additions - result.ks_state_subtractions) and (0.0); set result.ks_base_tax = result.ks_taxable_income * result.ks_corp_tax_base_rate; set result.ks_surtax = 0.0; set result.ks_tax_liability = the maximum of (result.ks_base_tax - result.ks_state_credits) and (0.0); set result.ks_refund_or_owed = result.ks_estimated_payments - result.ks_tax_liability; add "Kansas taxable income: $" + string value of (result.ks_taxable_income) to job.audit_trail; add "Kansas tax liability (4.0%): $" + string value of (result.ks_tax_liability) to job.audit_trail;</t>
+    <t>set ks_result.taxable_income = the maximum of (ks_result.apportioned_income + ks_result.state_additions - ks_result.state_subtractions) and (0.0); set ks_result.base_tax = ks_result.taxable_income * ks_result.corp_tax_base_rate; set ks_result.surtax = 0.0; set ks_result.tax_liability = the maximum of (ks_result.base_tax - ks_result.state_credits) and (0.0); set ks_result.refund_or_owed = ks_result.estimated_payments - ks_result.tax_liability; add "Kansas taxable income: $" + string value of (ks_result.taxable_income) to job.audit_trail; add "Kansas tax liability (4.0%): $" + string value of (ks_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.ks_taxable_income = 0.0; set result.ks_tax_liability = 0.0;</t>
+    <t>set ks_result.taxable_income = 0.0; set ks_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -217,13 +217,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>result</t>
+    <t>ks_result</t>
   </si>
   <si>
     <t>(25 attributes)</t>
   </si>
   <si>
-    <t>ks_apportioned_income</t>
+    <t>apportioned_income</t>
   </si>
   <si>
     <t>double</t>
@@ -238,7 +238,7 @@
     <t>Declared from decision-table usage; referenced by KS but never declared (campaign #948 Phase 1)</t>
   </si>
   <si>
-    <t>ks_apportionment_formula</t>
+    <t>apportionment_formula</t>
   </si>
   <si>
     <t>string</t>
@@ -250,13 +250,13 @@
     <t>KS uses three-factor apportionment (property, payroll, sales) with optional two-factor; single-sales for 2027+</t>
   </si>
   <si>
-    <t>ks_base_tax</t>
+    <t>base_tax</t>
   </si>
   <si>
     <t>KS base tax at 4.0% on all income</t>
   </si>
   <si>
-    <t>ks_corp_tax_base_rate</t>
+    <t>corp_tax_base_rate</t>
   </si>
   <si>
     <t>0.04</t>
@@ -265,7 +265,7 @@
     <t>KS corporate income tax base rate: 4.0% (includes 0.5% temporary increase, K.S.A. 79-32,110)</t>
   </si>
   <si>
-    <t>ks_corp_tax_rate</t>
+    <t>corp_tax_rate</t>
   </si>
   <si>
     <t>0.07</t>
@@ -274,7 +274,7 @@
     <t>KS effective combined rate: 7.0% (4.0% base + 3.0% surtax) on income over $50,000</t>
   </si>
   <si>
-    <t>ks_corp_tax_surtax_rate</t>
+    <t>corp_tax_surtax_rate</t>
   </si>
   <si>
     <t>0.03</t>
@@ -283,7 +283,7 @@
     <t>KS corporate income tax surtax: 3.0% on income over $50,000 (K.S.A. 79-32,110)</t>
   </si>
   <si>
-    <t>ks_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>100000.0</t>
@@ -292,13 +292,13 @@
     <t>KS economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
-    <t>ks_estimated_payments</t>
-  </si>
-  <si>
-    <t>ks_gross_receipts</t>
-  </si>
-  <si>
-    <t>ks_has_nexus</t>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
   </si>
   <si>
     <t>boolean</t>
@@ -310,55 +310,55 @@
     <t>Whether corporation has nexus with Kansas</t>
   </si>
   <si>
-    <t>ks_income_above_threshold</t>
+    <t>income_above_threshold</t>
   </si>
   <si>
     <t>KS taxable income above $50,000 surtax threshold (subject to surtax)</t>
   </si>
   <si>
-    <t>ks_income_below_threshold</t>
+    <t>income_below_threshold</t>
   </si>
   <si>
     <t>KS taxable income below $50,000 surtax threshold</t>
   </si>
   <si>
-    <t>ks_municipal_interest</t>
-  </si>
-  <si>
-    <t>ks_refund_or_owed</t>
-  </si>
-  <si>
-    <t>ks_state_additions</t>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
+    <t>state_additions</t>
   </si>
   <si>
     <t>KS additions to federal taxable income (federal interest income, state income tax refunds, IRC 163(j) adjustments, etc.)</t>
   </si>
   <si>
-    <t>ks_state_credits</t>
+    <t>state_credits</t>
   </si>
   <si>
     <t>KS tax credits (job creation, film production, historic preservation, community service contribution, etc.)</t>
   </si>
   <si>
-    <t>ks_state_subtractions</t>
+    <t>state_subtractions</t>
   </si>
   <si>
     <t>KS subtractions from federal taxable income (Kansas municipal bond interest, state income taxes paid, Kansas NOL, etc.)</t>
   </si>
   <si>
-    <t>ks_state_tax_refunds</t>
-  </si>
-  <si>
-    <t>ks_state_taxes_paid</t>
-  </si>
-  <si>
-    <t>ks_surtax</t>
+    <t>state_tax_refunds</t>
+  </si>
+  <si>
+    <t>state_taxes_paid</t>
+  </si>
+  <si>
+    <t>surtax</t>
   </si>
   <si>
     <t>KS surtax at 3.0% on income above $50,000</t>
   </si>
   <si>
-    <t>ks_surtax_threshold</t>
+    <t>surtax_threshold</t>
   </si>
   <si>
     <t>50000.0</t>
@@ -367,19 +367,19 @@
     <t>KS surtax threshold: $50,000 - surtax applies to income above this amount</t>
   </si>
   <si>
-    <t>ks_tax_liability</t>
+    <t>tax_liability</t>
   </si>
   <si>
     <t>KS corporate income tax liability</t>
   </si>
   <si>
-    <t>ks_taxable_income</t>
+    <t>taxable_income</t>
   </si>
   <si>
     <t>KS taxable income after apportionment and modifications</t>
   </si>
   <si>
-    <t>ks_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -391,7 +391,7 @@
     <t>KS economic nexus transaction count threshold: 200 transactions</t>
   </si>
   <si>
-    <t>ks_us_interest_income</t>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
